--- a/simulations/correction_peat_market/AS_taux de tri/AS_pos_ssinv_all.xlsx
+++ b/simulations/correction_peat_market/AS_taux de tri/AS_pos_ssinv_all.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_taux de tri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE84CFAD-F1AA-4D20-A322-55865B7F3F82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B5884B-CE75-49CC-8EF3-A16CD24C871F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
@@ -237,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -256,6 +259,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -271,6 +283,41 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Contrainte de capacité"/>
+      <sheetName val="results"/>
+      <sheetName val="Feuil1"/>
+      <sheetName val="Feuil2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="AD3">
+            <v>-544740.82216742123</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AE4">
+            <v>-483581.00663625158</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AF5">
+            <v>-3.716445296378966</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -558,9 +605,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO9"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="30" max="30" width="9.08984375" customWidth="1"/>
+    <col min="31" max="31" width="12.36328125" customWidth="1"/>
+    <col min="32" max="32" width="13.08984375" customWidth="1"/>
+    <col min="33" max="33" width="11.6328125" customWidth="1"/>
+    <col min="34" max="34" width="9.7265625" customWidth="1"/>
     <col min="36" max="36" width="13.6328125" customWidth="1"/>
     <col min="37" max="37" width="11.6328125" customWidth="1"/>
     <col min="38" max="38" width="12.54296875" customWidth="1"/>
@@ -602,14 +654,14 @@
       <c r="AB1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="6"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="10"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -1218,12 +1270,25 @@
         <v>100.00999999999999</v>
       </c>
     </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="AD11" s="4">
+        <f>(AD3-[1]results!$AD$3)/[1]results!$AD$3</f>
+        <v>0.35215944879792588</v>
+      </c>
+      <c r="AE11" s="4">
+        <f>(AE4-[1]results!$AE$4)/[1]results!$AE$4</f>
+        <v>0.3963895341354462</v>
+      </c>
+      <c r="AF11" s="4">
+        <f>(AF5-[1]results!$AF$5)/[1]results!$AF$5</f>
+        <v>0.6998841865434976</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:Y1"/>
     <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AC1:AH1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
